--- a/survey_templates/045_online_social_networking_questionnaire--survey_templates.xlsx
+++ b/survey_templates/045_online_social_networking_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -862,12 +862,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>favorite_online_shops</t>
+          <t>favorite_online_shops_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Favorite Online Shops</t>
+          <t>Favorite Online Shops 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_per_month</t>
+          <t>online_shopping_frequency_per_month_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Online Shopping Frequency Per Month</t>
+          <t>Online Shopping Frequency Per Month 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>online_shopping_frequency</t>
+          <t>online_shopping_frequency_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Online Shopping Frequency</t>
+          <t>Online Shopping Frequency 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1122,8 +1122,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option1':_'daily'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option1': 'Daily'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option2':_'weekly'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option2': 'Weekly'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option3':_'monthly'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option3': 'Monthly'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option4':_'rarely'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option4': 'Rarely'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option5':_'never'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option5': 'Never'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option1':_'gmail'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option1': 'Gmail'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option2':_'yahoo'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option2': 'Yahoo'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option3':_'aol'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option3': 'AOL'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option4':_'hotmail'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option4': 'Hotmail'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option5':_'other'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option5': 'Other'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option6':_'none'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option6': 'None'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option1':_'verizon'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option1': 'Verizon'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option2':_'tmobile'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option2': 'TMobile'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option3':_'at&amp;t'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option3': 'AT&amp;T'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'option4':_'other'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'option4': 'Other'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'option5':_'none'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'option5': 'None'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'option1':_'1-5'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'option1': '1-5'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'option2':_'6-10'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'option2': '6-10'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'option3':_'11-15'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'option3': '11-15'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'option4':_'16-20'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'option4': '16-20'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'option5':_'more_than_20'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'option5': 'More than 20'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'option1':_'1-2'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'option1': '1-2'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'option2':_'3-5'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'option2': '3-5'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'option3':_'6-7'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'option3': '6-7'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'option4':_'daily'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'option4': 'Daily'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1746,19 +1746,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'option5':_'never'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'option5': 'Never'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>favorite_online_shops_choices</t>
+          <t>favorite_online_shops_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1775,7 +1775,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>favorite_online_shops_choices</t>
+          <t>favorite_online_shops_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'option1':_'never'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'option1': 'Never'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'option2':_'1-5'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'option2': '1-5'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'option3':_'6-10'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'option3': '6-10'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1882,12 +1882,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'option4':_'11-15'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'option4': '11-15'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'option5':_'16-30'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'option5': '16-30'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1916,12 +1916,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'option1':_'never'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'option1': 'Never'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'option2':_'1-2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'option2': '1-2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'option3':_'3-5'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'option3': '3-5'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1967,12 +1967,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'option4':_'6-7'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'option4': '6-7'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'option1':_'less_than_10'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'option1': 'Less than 10'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'option2':_'10-30'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'option2': '10-30'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'option3':_'30-60'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'option3': '30-60'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2035,97 +2035,97 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'option4':_'more_than_60'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'option4': 'More than 60'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_per_month_choices</t>
+          <t>online_shopping_frequency_per_month_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'option1':_'less_than_5'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'option1': 'Less than 5'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_per_month_choices</t>
+          <t>online_shopping_frequency_per_month_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'option2':_'5-10'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'option2': '5-10'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_per_month_choices</t>
+          <t>online_shopping_frequency_per_month_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'option3':_'11-20'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'option3': '11-20'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_per_month_choices</t>
+          <t>online_shopping_frequency_per_month_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'option4':_'21-30'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'option4': '21-30'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_per_month_choices</t>
+          <t>online_shopping_frequency_per_month_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'option5':_'more_than_30'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'option5': 'More than 30'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -2137,12 +2137,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'option1':_'1-2'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'option1': '1-2'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'option2':_'3-4'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'option2': '3-4'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'option3':_'5-6'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'option3': '5-6'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'option4':_'more_than_6'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'option4': 'More than 6'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'option1':_'less_than_2'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'option1': 'Less than 2'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2222,12 +2222,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'option2':_'2-4'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'option2': '2-4'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'option3':_'5-6'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'option3': '5-6'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2256,97 +2256,97 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'option4':_'more_than_6'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'option4': 'More than 6'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_choices</t>
+          <t>online_shopping_frequency_2_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'option1':_'daily'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'option1': 'Daily'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_choices</t>
+          <t>online_shopping_frequency_2_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'option2':_'weekly'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'option2': 'Weekly'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_choices</t>
+          <t>online_shopping_frequency_2_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'option3':_'monthly'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'option3': 'Monthly'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_choices</t>
+          <t>online_shopping_frequency_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'option4':_'rarely'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'option4': 'Rarely'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>online_shopping_frequency_choices</t>
+          <t>online_shopping_frequency_2_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'option5':_'never'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'option5': 'Never'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
